--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -11349,6 +11349,150 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11382,7 +11526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11609,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -11475,7 +11619,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -761,9 +761,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -905,9 +902,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -2345,9 +2339,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2489,9 +2480,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3785,9 +3773,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -3929,9 +3914,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5225,9 +5207,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5369,9 +5348,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6665,9 +6641,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -6809,9 +6782,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8393,9 +8363,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -8537,9 +8504,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -8681,9 +8645,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -8825,9 +8786,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -8969,9 +8927,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9113,9 +9068,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -9257,9 +9209,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9401,9 +9350,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -9545,9 +9491,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -9689,9 +9632,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -9833,9 +9773,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -9977,9 +9914,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10121,9 +10055,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10265,9 +10196,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -10409,9 +10337,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10553,9 +10478,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -10697,9 +10619,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -10841,9 +10760,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -10985,9 +10901,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11129,9 +11042,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -11273,9 +11183,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -11415,9 +11322,6 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -11397,6 +11397,147 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11430,7 +11571,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -11523,7 +11664,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -11538,6 +11538,147 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11571,7 +11712,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11795,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -11664,7 +11805,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -9733,12 +9733,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9807,42 +9807,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9874,12 +9874,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9900,7 +9900,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -9948,42 +9948,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10015,12 +10015,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10089,42 +10089,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10156,12 +10156,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10182,7 +10182,7 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -10230,42 +10230,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10297,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10371,42 +10371,42 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10464,7 +10464,7 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -10512,42 +10512,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10579,12 +10579,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10653,42 +10653,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10720,12 +10720,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10746,7 +10746,7 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -10794,42 +10794,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10935,42 +10935,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11002,12 +11002,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11028,7 +11028,7 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -11076,42 +11076,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11143,12 +11143,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11169,12 +11169,12 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11217,42 +11217,42 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11284,12 +11284,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11310,7 +11310,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -11358,42 +11358,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -11592,7 +11592,7 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -11674,6 +11674,147 @@
         </is>
       </c>
       <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -11795,7 +11936,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -11805,7 +11946,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -11820,6 +11820,288 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11853,7 +12135,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11936,7 +12218,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -11946,7 +12228,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
